--- a/data/trans_dic/IP2004-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP2004-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores a los que les sangran las encías</t>
+          <t>Menores a los que les sangran las encías (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,47; 6,64</t>
+          <t>1,46; 6,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,21; 7,12</t>
+          <t>1,19; 6,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,77; 9,44</t>
+          <t>1,67; 9,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,9; 6,53</t>
+          <t>1,65; 6,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,93; 8,76</t>
+          <t>2,03; 8,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 5,76</t>
+          <t>1,01; 6,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 6,8</t>
+          <t>0,6; 6,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,99; 5,64</t>
+          <t>2,15; 5,94</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,15; 6,46</t>
+          <t>2,25; 6,62</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,05; 6,65</t>
+          <t>1,87; 6,03</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,28</t>
+          <t>0,36; 3,18</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,68; 7,39</t>
+          <t>2,4; 7,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,96</t>
+          <t>1,28; 5,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,15</t>
+          <t>0,94; 4,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,09; 5,6</t>
+          <t>1,19; 5,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,97; 6,25</t>
+          <t>1,97; 6,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,46</t>
+          <t>0,62; 3,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,23</t>
+          <t>0,34; 3,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 5,43</t>
+          <t>1,26; 5,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,7; 6,06</t>
+          <t>2,71; 6,05</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,62</t>
+          <t>1,21; 3,57</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,95</t>
+          <t>0,92; 2,99</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,56; 4,36</t>
+          <t>1,61; 4,67</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,86; 7,01</t>
+          <t>1,47; 6,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,9</t>
+          <t>0,47; 5,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 5,07</t>
+          <t>0,89; 5,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,6</t>
+          <t>0,19; 2,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 6,34</t>
+          <t>1,36; 6,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 4,6</t>
+          <t>0,4; 4,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,41</t>
+          <t>0,36; 2,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,48</t>
+          <t>0,63; 4,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,99; 5,45</t>
+          <t>2,05; 5,5</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,68</t>
+          <t>0,93; 4,05</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,31</t>
+          <t>0,87; 3,29</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,53</t>
+          <t>0,58; 2,6</t>
         </is>
       </c>
     </row>
@@ -1141,57 +1142,57 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,35; 7,81</t>
+          <t>2,36; 7,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,88</t>
+          <t>0,88; 5,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,6</t>
+          <t>0,0; 3,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,56</t>
+          <t>0,88; 4,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,83</t>
+          <t>0,96; 5,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,48</t>
+          <t>0,38; 3,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,74</t>
+          <t>0,63; 4,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,67</t>
+          <t>1,21; 3,82</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,09; 5,26</t>
+          <t>2,0; 5,24</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,45</t>
+          <t>0,98; 3,35</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,83</t>
+          <t>0,57; 3,29</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,37; 4,76</t>
+          <t>2,41; 4,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,21; 4,4</t>
+          <t>2,1; 4,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,05</t>
+          <t>1,89; 4,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,19</t>
+          <t>0,61; 2,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,24; 4,35</t>
+          <t>2,21; 4,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,72</t>
+          <t>1,55; 3,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,5</t>
+          <t>0,94; 2,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 3,43</t>
+          <t>1,46; 3,5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,6; 4,1</t>
+          <t>2,59; 4,15</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,14; 3,63</t>
+          <t>2,05; 3,59</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,57; 2,94</t>
+          <t>1,61; 2,96</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,18; 2,53</t>
+          <t>1,22; 2,48</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores a los que les sangran las encías (tasa de respuesta: 99,68%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>4502</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4509</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5883</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>5195</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>6408</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>3921</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>3292</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>9698</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>10917</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>9803</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>3292</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1889; 8980</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1584; 9222</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2076; 11784</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2352; 9792</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2881; 12120</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1404; 8472</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>826; 8406</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>5843; 16162</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>6199; 18224</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4922; 15906</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>904; 7997</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>8411</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5095</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4246</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4921</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>7369</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3695</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2814</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>6837</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>15780</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>8791</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>7060</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>11758</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>4464; 13643</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2439; 9688</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1824; 8089</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2221; 9769</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>4007; 12707</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1313; 7549</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>721; 7487</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>3127; 13412</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>10553; 23544</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>4888; 14367</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3717; 12074</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>7005; 20357</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>4935</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2944</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3777</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1529</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>4440</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2489</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1909</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>3378</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>9376</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>5433</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5687</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>4907</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1920; 8821</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>685; 7441</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1312; 7483</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>366; 4369</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1862; 8670</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>607; 6664</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>583; 4763</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1154; 8276</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>5484; 14707</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2750; 12039</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2681; 10167</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2159; 9677</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8407</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4686</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>4544</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>4527</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2805</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>3550</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>8746</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>12934</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>7491</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>4750</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>1595; 9584</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>4565; 15148</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1685; 9812</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 6422</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1736; 9765</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1880; 10209</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>718; 7240</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1119; 8308</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>4772; 15102</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>7788; 20435</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>3769; 12849</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>1945; 11307</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>22051</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>20955</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>18592</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>7651</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>21548</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>17120</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>11449</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>17057</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>43599</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>38075</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>30040</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>24707</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>15475; 30453</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>13929; 29559</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>12479; 26752</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>3971; 14928</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>15049; 29460</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>10853; 25767</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>6607; 17323</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>10934; 26191</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>34325; 54994</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>28013; 48995</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>21945; 40238</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>17140; 34804</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP2004-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP2004-Habitat-trans_dic.xlsx
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,46; 6,96</t>
+          <t>1,44; 7,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 6,93</t>
+          <t>1,51; 7,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,67; 9,45</t>
+          <t>1,93; 8,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,42 +737,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,65; 6,85</t>
+          <t>1,96; 6,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 8,53</t>
+          <t>2,12; 8,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 6,09</t>
+          <t>1,01; 6,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 6,15</t>
+          <t>0,62; 5,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,15; 5,94</t>
+          <t>2,04; 5,46</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,25; 6,62</t>
+          <t>2,01; 6,2</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,87; 6,03</t>
+          <t>1,99; 6,28</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,18</t>
+          <t>0,36; 3,19</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,4; 7,34</t>
+          <t>2,47; 7,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,28; 5,08</t>
+          <t>1,28; 4,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,18</t>
+          <t>0,93; 4,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 5,23</t>
+          <t>1,24; 5,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,97; 6,24</t>
+          <t>1,97; 6,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,57</t>
+          <t>0,61; 3,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,55</t>
+          <t>0,34; 3,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 5,38</t>
+          <t>1,15; 5,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,71; 6,05</t>
+          <t>2,71; 5,79</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,57</t>
+          <t>1,22; 3,53</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,99</t>
+          <t>0,93; 3,05</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,67</t>
+          <t>1,61; 4,45</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 6,77</t>
+          <t>1,46; 7,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 5,14</t>
+          <t>0,47; 4,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 5,05</t>
+          <t>1,04; 5,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,32</t>
+          <t>0,19; 2,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 6,32</t>
+          <t>1,4; 6,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 4,38</t>
+          <t>0,4; 4,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,97</t>
+          <t>0,36; 3,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 4,51</t>
+          <t>0,59; 4,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 5,5</t>
+          <t>1,91; 5,87</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,05</t>
+          <t>0,81; 3,75</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,29</t>
+          <t>0,83; 3,5</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,6</t>
+          <t>0,57; 2,58</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,84</t>
+          <t>0,78; 4,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,36; 7,83</t>
+          <t>2,2; 7,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,1</t>
+          <t>0,86; 4,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,87</t>
+          <t>0,0; 4,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,95</t>
+          <t>0,99; 4,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 5,2</t>
+          <t>0,96; 4,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,8</t>
+          <t>0,38; 3,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 4,67</t>
+          <t>0,66; 4,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,82</t>
+          <t>1,23; 3,82</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,0; 5,24</t>
+          <t>1,99; 5,04</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,35</t>
+          <t>1,03; 3,61</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,29</t>
+          <t>0,56; 2,94</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,41; 4,73</t>
+          <t>2,34; 4,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,46</t>
+          <t>2,2; 4,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,06</t>
+          <t>1,91; 4,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,28</t>
+          <t>0,61; 2,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,21; 4,33</t>
+          <t>2,25; 4,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,55; 3,67</t>
+          <t>1,52; 3,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,47</t>
+          <t>0,97; 2,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,5</t>
+          <t>1,44; 3,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,59; 4,15</t>
+          <t>2,64; 4,17</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,05; 3,59</t>
+          <t>2,07; 3,64</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,96</t>
+          <t>1,66; 2,97</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,48</t>
+          <t>1,15; 2,55</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1889; 8980</t>
+          <t>1863; 9096</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1584; 9222</t>
+          <t>2005; 9723</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2076; 11784</t>
+          <t>2402; 10965</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1665,42 +1665,42 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2352; 9792</t>
+          <t>2803; 9903</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2881; 12120</t>
+          <t>3009; 12302</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1404; 8472</t>
+          <t>1410; 8728</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>826; 8406</t>
+          <t>846; 8161</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5843; 16162</t>
+          <t>5554; 14841</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6199; 18224</t>
+          <t>5535; 17064</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4922; 15906</t>
+          <t>5257; 16563</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>904; 7997</t>
+          <t>898; 8041</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4464; 13643</t>
+          <t>4595; 13111</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2439; 9688</t>
+          <t>2444; 9353</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1824; 8089</t>
+          <t>1805; 8384</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2221; 9769</t>
+          <t>2312; 10302</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4007; 12707</t>
+          <t>4003; 12717</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1313; 7549</t>
+          <t>1290; 8090</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>721; 7487</t>
+          <t>710; 6502</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3127; 13412</t>
+          <t>2857; 13553</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10553; 23544</t>
+          <t>10558; 22544</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4888; 14367</t>
+          <t>4916; 14196</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3717; 12074</t>
+          <t>3751; 12314</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7005; 20357</t>
+          <t>7029; 19405</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1920; 8821</t>
+          <t>1899; 9328</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>685; 7441</t>
+          <t>680; 7063</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1312; 7483</t>
+          <t>1535; 8025</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>366; 4369</t>
+          <t>356; 4057</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1862; 8670</t>
+          <t>1925; 8322</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>607; 6664</t>
+          <t>613; 7110</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>583; 4763</t>
+          <t>581; 5096</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1154; 8276</t>
+          <t>1092; 8065</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5484; 14707</t>
+          <t>5107; 15697</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2750; 12039</t>
+          <t>2408; 11129</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2681; 10167</t>
+          <t>2575; 10813</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2159; 9677</t>
+          <t>2107; 9577</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1595; 9584</t>
+          <t>1536; 9051</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4565; 15148</t>
+          <t>4254; 14882</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1685; 9812</t>
+          <t>1655; 9175</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 6422</t>
+          <t>0; 6742</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1736; 9765</t>
+          <t>1958; 9408</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1880; 10209</t>
+          <t>1883; 9580</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>718; 7240</t>
+          <t>717; 6916</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1119; 8308</t>
+          <t>1179; 8412</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4772; 15102</t>
+          <t>4874; 15110</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7788; 20435</t>
+          <t>7749; 19638</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3769; 12849</t>
+          <t>3941; 13818</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1945; 11307</t>
+          <t>1933; 10114</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>15475; 30453</t>
+          <t>15021; 30106</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>13929; 29559</t>
+          <t>14564; 29592</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12479; 26752</t>
+          <t>12574; 27149</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3971; 14928</t>
+          <t>4007; 13380</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>15049; 29460</t>
+          <t>15282; 29798</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10853; 25767</t>
+          <t>10646; 25644</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6607; 17323</t>
+          <t>6782; 17999</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10934; 26191</t>
+          <t>10765; 25750</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>34325; 54994</t>
+          <t>34895; 55184</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28013; 48995</t>
+          <t>28308; 49648</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21945; 40238</t>
+          <t>22538; 40371</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>17140; 34804</t>
+          <t>16155; 35730</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2004-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP2004-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,44 +649,44 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3,64%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4,51%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>3,49%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3,39%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>4,72%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,64%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,51%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
           <t>3,57%</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,44; 7,05</t>
+          <t>1,9; 6,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 7,3</t>
+          <t>1,93; 8,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,93; 8,8</t>
+          <t>1,0; 5,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>0,64; 6,53</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1,47; 6,64</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,21; 7,12</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1,77; 9,44</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1,96; 6,93</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2,12; 8,66</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1,01; 6,27</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0,62; 5,97</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,04; 5,46</t>
+          <t>1,99; 5,64</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,01; 6,2</t>
+          <t>2,15; 6,46</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,99; 6,28</t>
+          <t>2,05; 6,65</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,19</t>
+          <t>0,31; 3,21</t>
         </is>
       </c>
     </row>
@@ -789,62 +789,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3,62%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>4,53%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2,67%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2,2%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,62%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>4,05%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>1,75%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2,74%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>4,05%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,47; 7,06</t>
+          <t>1,97; 6,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,9</t>
+          <t>0,6; 3,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,34</t>
+          <t>0,34; 3,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 5,51</t>
+          <t>1,09; 4,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,97; 6,25</t>
+          <t>2,68; 7,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,83</t>
+          <t>1,35; 4,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,09</t>
+          <t>0,93; 4,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,15; 5,44</t>
+          <t>1,13; 6,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,71; 5,79</t>
+          <t>2,7; 6,06</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,53</t>
+          <t>1,24; 3,62</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,05</t>
+          <t>0,89; 2,95</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,45</t>
+          <t>1,55; 4,38</t>
         </is>
       </c>
     </row>
@@ -929,62 +929,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3,24%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>3,79%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2,04%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2,55%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>3,51%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
           <t>1,84%</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>3,51%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 7,16</t>
+          <t>1,31; 6,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,88</t>
+          <t>0,4; 4,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 5,42</t>
+          <t>0,37; 3,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,16</t>
+          <t>0,55; 4,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 6,07</t>
+          <t>1,86; 7,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 4,67</t>
+          <t>0,46; 4,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,18</t>
+          <t>0,86; 5,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 4,39</t>
+          <t>0,23; 3,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 5,87</t>
+          <t>1,99; 5,45</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,75</t>
+          <t>0,73; 3,68</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,5</t>
+          <t>0,88; 3,31</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,58</t>
+          <t>0,63; 3,06</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1,98%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>2,12%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>4,34%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>2,43%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,57</t>
+          <t>0,8; 4,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,2; 7,69</t>
+          <t>0,96; 4,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 4,77</t>
+          <t>0,38; 3,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,06</t>
+          <t>0,8; 4,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,77</t>
+          <t>0,8; 4,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,88</t>
+          <t>2,35; 7,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,63</t>
+          <t>0,87; 4,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,73</t>
+          <t>0,0; 3,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,82</t>
+          <t>1,19; 3,67</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,99; 5,04</t>
+          <t>2,09; 5,26</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,61</t>
+          <t>0,95; 3,45</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,94</t>
+          <t>0,54; 2,89</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>3,17%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>3,43%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>3,16%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>2,82%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,34; 4,68</t>
+          <t>2,24; 4,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,47</t>
+          <t>1,6; 3,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,12</t>
+          <t>1,0; 2,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,04</t>
+          <t>1,51; 3,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,25; 4,38</t>
+          <t>2,37; 4,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,65</t>
+          <t>2,21; 4,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,57</t>
+          <t>1,87; 4,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,44</t>
+          <t>0,65; 2,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,64; 4,17</t>
+          <t>2,6; 4,1</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,07; 3,64</t>
+          <t>2,14; 3,63</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,97</t>
+          <t>1,57; 2,94</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,55</t>
+          <t>1,22; 2,6</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,44 +1577,44 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5195</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6408</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3921</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2994</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>4502</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>4509</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>5883</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>5195</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6408</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>3921</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>3292</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
           <t>9698</t>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3292</t>
+          <t>2994</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1863; 9096</t>
+          <t>2721; 9333</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2005; 9723</t>
+          <t>2744; 12444</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2402; 10965</t>
+          <t>1394; 8013</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>792; 8019</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1891; 8571</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1616; 9488</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2201; 11775</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2803; 9903</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3009; 12302</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1410; 8728</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>846; 8161</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5554; 14841</t>
+          <t>5403; 15339</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5535; 17064</t>
+          <t>5920; 17777</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5257; 16563</t>
+          <t>5396; 17553</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>898; 8041</t>
+          <t>748; 7763</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7369</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3695</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2814</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5994</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>8411</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>5095</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>4246</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4921</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7369</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3695</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2814</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6837</t>
+          <t>5222</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11758</t>
+          <t>11216</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4595; 13111</t>
+          <t>4005; 12719</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2444; 9353</t>
+          <t>1267; 7321</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1805; 8384</t>
+          <t>712; 6813</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2312; 10302</t>
+          <t>2530; 11329</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4003; 12717</t>
+          <t>4970; 13727</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1290; 8090</t>
+          <t>2582; 9458</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>710; 6502</t>
+          <t>1795; 8018</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2857; 13553</t>
+          <t>2049; 11150</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10558; 22544</t>
+          <t>10516; 23599</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4916; 14196</t>
+          <t>4994; 14568</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3751; 12314</t>
+          <t>3610; 11928</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7029; 19405</t>
+          <t>6416; 18130</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>4440</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2489</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1909</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3348</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>4935</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>2944</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>3777</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1529</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>4440</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2489</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1909</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3378</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4907</t>
+          <t>4844</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1899; 9328</t>
+          <t>1794; 8694</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>680; 7063</t>
+          <t>603; 7004</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1535; 8025</t>
+          <t>586; 5469</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>356; 4057</t>
+          <t>917; 8054</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1925; 8322</t>
+          <t>2423; 9121</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>613; 7110</t>
+          <t>672; 7083</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>581; 5096</t>
+          <t>1275; 7518</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1092; 8065</t>
+          <t>356; 4832</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5107; 15697</t>
+          <t>5329; 14582</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2408; 11129</t>
+          <t>2171; 10915</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2575; 10813</t>
+          <t>2722; 10221</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2107; 9577</t>
+          <t>2033; 9838</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4544</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4527</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2805</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3291</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>4202</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>8407</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>4686</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4544</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4527</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2805</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3550</t>
+          <t>1237</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>4528</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1536; 9051</t>
+          <t>1576; 8985</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4254; 14882</t>
+          <t>1875; 9488</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1655; 9175</t>
+          <t>717; 6644</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 6742</t>
+          <t>1337; 8161</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1958; 9408</t>
+          <t>1579; 9583</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1883; 9580</t>
+          <t>4541; 15118</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>717; 6916</t>
+          <t>1668; 9397</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1179; 8412</t>
+          <t>0; 6085</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4874; 15110</t>
+          <t>4692; 14494</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7749; 19638</t>
+          <t>8145; 20502</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3941; 13818</t>
+          <t>3645; 13223</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1933; 10114</t>
+          <t>1776; 9581</t>
         </is>
       </c>
     </row>
@@ -2346,37 +2346,37 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>21548</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>17120</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>11449</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>15627</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>22051</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>20955</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>18592</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>7651</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>21548</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>17120</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>11449</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>17057</t>
+          <t>7955</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>24707</t>
+          <t>23583</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>15021; 30106</t>
+          <t>15280; 29635</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>14564; 29592</t>
+          <t>11243; 26097</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12574; 27149</t>
+          <t>6984; 17556</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4007; 13380</t>
+          <t>10377; 23077</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>15282; 29798</t>
+          <t>15223; 30597</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10646; 25644</t>
+          <t>14641; 29159</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6782; 17999</t>
+          <t>12341; 26686</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10765; 25750</t>
+          <t>4007; 14589</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>34895; 55184</t>
+          <t>34429; 54328</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28308; 49648</t>
+          <t>29207; 49547</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22538; 40371</t>
+          <t>21326; 39957</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16155; 35730</t>
+          <t>15940; 34073</t>
         </is>
       </c>
     </row>
